--- a/volumes/02-solar-home-systems/templates/AEF_V2_T04_Agent_Economics.xlsx
+++ b/volumes/02-solar-home-systems/templates/AEF_V2_T04_Agent_Economics.xlsx
@@ -566,7 +566,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AFRICA ENERGY FINANCE  |  VOLUME 2  |  SOLAR HOME SYSTEMS</t>
+          <t>AFRICA ENERGY FINANCE  |  BOOK 2  |  PAYGO SOLAR FINANCE</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Template T04  |  Version 1.0  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
+          <t>Template T04  |  Version 0.9 (pre-release)  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -759,7 +759,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Links to the Volume 2 model and book</t>
+          <t>Links to Book 2 and MODEL 2</t>
         </is>
       </c>
       <c r="B23" s="6" t="n"/>
@@ -808,7 +808,7 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>Decision support material; not investment, legal, tax or accounting advice. Example values are illustrative and refer to the fictional SolaraPay case where data are needed. (c) 2026 Emmanuel Boujieka Kamga.</t>
+          <t>Decision support material; not investment, legal, tax or accounting advice. Example values are illustrative and refer to the book's worked examples or to the fictional SolaraPay case. (c) 2026 Emmanuel Boujieka Kamga.</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Volume 2 Template T04&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Book 2 Template T04 | Version 0.9 (pre-release)&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -863,7 +863,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AFRICA ENERGY FINANCE  |  VOLUME 2  |  SOLAR HOME SYSTEMS</t>
+          <t>AFRICA ENERGY FINANCE  |  BOOK 2  |  PAYGO SOLAR FINANCE</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -905,7 +905,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Template T04  |  Version 1.0  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
+          <t>Template T04  |  Version 0.9 (pre-release)  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -1313,7 +1313,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Volume 2 Template T04&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Book 2 Template T04 | Version 0.9 (pre-release)&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1344,7 +1344,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AFRICA ENERGY FINANCE  |  VOLUME 2  |  SOLAR HOME SYSTEMS</t>
+          <t>AFRICA ENERGY FINANCE  |  BOOK 2  |  PAYGO SOLAR FINANCE</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1386,7 +1386,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Template T04  |  Version 1.0  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
+          <t>Template T04  |  Version 0.9 (pre-release)  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -1921,7 +1921,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Volume 2 Template T04&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Book 2 Template T04 | Version 0.9 (pre-release)&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1956,7 +1956,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AFRICA ENERGY FINANCE  |  VOLUME 2  |  SOLAR HOME SYSTEMS</t>
+          <t>AFRICA ENERGY FINANCE  |  BOOK 2  |  PAYGO SOLAR FINANCE</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2010,7 +2010,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Template T04  |  Version 1.0  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
+          <t>Template T04  |  Version 0.9 (pre-release)  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="F6" s="18" t="inlineStr">
         <is>
-          <t>Repayment rate at month 6</t>
+          <t>Repayment ratio at month 6</t>
         </is>
       </c>
       <c r="G6" s="18" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>Minimum repayment rate at month 6</t>
+          <t>Minimum repayment ratio at month 6</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>Repayment rate for top commission band</t>
+          <t>Repayment ratio for top commission band</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="L26" s="15" t="inlineStr">
         <is>
-          <t>Example rows are randomly generated illustrations; replace them with company data.</t>
+          <t>Example rows are random illustrations; replace them with company data. Repayment ratio: cumulative collections ÷ instalments due at month 6 (a cohort ratio, not a PERFORM KPI).</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Volume 2 Template T04&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Book 2 Template T04 | Version 0.9 (pre-release)&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -3361,7 +3361,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AFRICA ENERGY FINANCE  |  VOLUME 2  |  SOLAR HOME SYSTEMS</t>
+          <t>AFRICA ENERGY FINANCE  |  BOOK 2  |  PAYGO SOLAR FINANCE</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3421,7 +3421,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Template T04  |  Version 1.0  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
+          <t>Template T04  |  Version 0.9 (pre-release)  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -3802,7 +3802,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Volume 2 Template T04&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Book 2 Template T04 | Version 0.9 (pre-release)&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
